--- a/docs/Plantilla_Rutina.xlsx
+++ b/docs/Plantilla_Rutina.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Rutina" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Ejercicios" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Metas" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Progreso" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Horario" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tareas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Ejercicios" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Hitos" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -42,7 +42,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F6FEB"/>
+        <fgColor rgb="004A7A5A"/>
       </patternFill>
     </fill>
   </fills>
@@ -72,12 +72,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -443,15 +442,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -477,7 +476,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Categoría</t>
+          <t>Contexto</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -489,59 +488,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Lunes</t>
+          <t>Jueves</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Estudio de arquitectura</t>
+          <t>Despertar</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Estudio</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Bloque profundo</t>
-        </is>
-      </c>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lunes</t>
+          <t>Jueves</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Calistenia - Empuje</t>
+          <t>Desayuno</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ejercicio</t>
+          <t>General</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -549,7 +536,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Martes</t>
+          <t>Jueves</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,12 +546,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Proyecto personal</t>
+          <t>Clases</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -572,43 +559,151 @@
           <t>Estudio</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Foco de la mañana</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Miércoles</t>
+          <t>Jueves</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Comida — fuerte</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Entrenamiento</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Calistenia</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Dormir</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Clases</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Estudio</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Calistenia - Tracción</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Ejercicio</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Entrenamiento</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Calistenia</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="A2:A200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A2:A100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Estudio,Ejercicio,Personal,Otro"</formula1>
+    <dataValidation sqref="E2:E100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Estudio,Calistenia,General"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -621,205 +716,149 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Contexto</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Día</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Hora</t>
-        </is>
-      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Ejercicio</t>
+          <t>Tarea</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Series</t>
+          <t>Estimación</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Reps</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Notas</t>
+          <t>Orden</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Lunes</t>
+          <t>Estudio</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>Jueves</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Flexiones</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Flexiones seguidas</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>Wireframes pantallas</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2h</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lunes</t>
+          <t>Estudio</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>Jueves</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fondos en paralelas</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>8-10</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+          <t>Revisión con mentor</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>45m</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Miércoles</t>
+          <t>Estudio</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>Jueves</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dominadas</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>6-8</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Dominadas seguidas</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>Ajustar propuesta</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Miércoles</t>
+          <t>Estudio</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>Lunes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remo australiano</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Viernes</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Plancha (hold)</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>30 seg</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Plancha 60s</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>Leer capítulo 3</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="A2:A200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="2">
+    <dataValidation sqref="A2:A100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Estudio,Calistenia"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B2:B100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
     </dataValidation>
   </dataValidations>
@@ -833,348 +872,183 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Día</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Tipo</t>
+          <t>Hora</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Actual</t>
+          <t>Ejercicio</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Objetivo</t>
+          <t>Series</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Unidad</t>
+          <t>Reps</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Fecha límite</t>
+          <t>Notas</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Dominadas seguidas</t>
+          <t>Jueves</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Calistenia</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>6</v>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Flexiones</t>
+        </is>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>reps</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Flexiones seguidas</t>
+          <t>Jueves</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Calistenia</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>20</v>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Fondos en paralelas</t>
+        </is>
       </c>
       <c r="D3" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>reps</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
+          <t>8-10</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Plancha 60s</t>
+          <t>Jueves</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Calistenia</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>30</v>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Dominadas</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>seg</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
+          <t>6-8</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Avance del proyecto</t>
+          <t>Lunes</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Proyecto</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>35</v>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Sentadillas</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Horas de estudio (mes)</t>
+          <t>Lunes</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Proyecto</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>12</v>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Plancha (hold)</t>
+        </is>
       </c>
       <c r="D6" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>horas</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="F7" s="2" t="n"/>
-    </row>
-    <row r="8">
-      <c r="F8" s="2" t="n"/>
-    </row>
-    <row r="9">
-      <c r="F9" s="2" t="n"/>
-    </row>
-    <row r="10">
-      <c r="F10" s="2" t="n"/>
-    </row>
-    <row r="11">
-      <c r="F11" s="2" t="n"/>
-    </row>
-    <row r="12">
-      <c r="F12" s="2" t="n"/>
-    </row>
-    <row r="13">
-      <c r="F13" s="2" t="n"/>
-    </row>
-    <row r="14">
-      <c r="F14" s="2" t="n"/>
-    </row>
-    <row r="15">
-      <c r="F15" s="2" t="n"/>
-    </row>
-    <row r="16">
-      <c r="F16" s="2" t="n"/>
-    </row>
-    <row r="17">
-      <c r="F17" s="2" t="n"/>
-    </row>
-    <row r="18">
-      <c r="F18" s="2" t="n"/>
-    </row>
-    <row r="19">
-      <c r="F19" s="2" t="n"/>
-    </row>
-    <row r="20">
-      <c r="F20" s="2" t="n"/>
-    </row>
-    <row r="21">
-      <c r="F21" s="2" t="n"/>
-    </row>
-    <row r="22">
-      <c r="F22" s="2" t="n"/>
-    </row>
-    <row r="23">
-      <c r="F23" s="2" t="n"/>
-    </row>
-    <row r="24">
-      <c r="F24" s="2" t="n"/>
-    </row>
-    <row r="25">
-      <c r="F25" s="2" t="n"/>
-    </row>
-    <row r="26">
-      <c r="F26" s="2" t="n"/>
-    </row>
-    <row r="27">
-      <c r="F27" s="2" t="n"/>
-    </row>
-    <row r="28">
-      <c r="F28" s="2" t="n"/>
-    </row>
-    <row r="29">
-      <c r="F29" s="2" t="n"/>
-    </row>
-    <row r="30">
-      <c r="F30" s="2" t="n"/>
-    </row>
-    <row r="31">
-      <c r="F31" s="2" t="n"/>
-    </row>
-    <row r="32">
-      <c r="F32" s="2" t="n"/>
-    </row>
-    <row r="33">
-      <c r="F33" s="2" t="n"/>
-    </row>
-    <row r="34">
-      <c r="F34" s="2" t="n"/>
-    </row>
-    <row r="35">
-      <c r="F35" s="2" t="n"/>
-    </row>
-    <row r="36">
-      <c r="F36" s="2" t="n"/>
-    </row>
-    <row r="37">
-      <c r="F37" s="2" t="n"/>
-    </row>
-    <row r="38">
-      <c r="F38" s="2" t="n"/>
-    </row>
-    <row r="39">
-      <c r="F39" s="2" t="n"/>
-    </row>
-    <row r="40">
-      <c r="F40" s="2" t="n"/>
-    </row>
-    <row r="41">
-      <c r="F41" s="2" t="n"/>
-    </row>
-    <row r="42">
-      <c r="F42" s="2" t="n"/>
-    </row>
-    <row r="43">
-      <c r="F43" s="2" t="n"/>
-    </row>
-    <row r="44">
-      <c r="F44" s="2" t="n"/>
-    </row>
-    <row r="45">
-      <c r="F45" s="2" t="n"/>
-    </row>
-    <row r="46">
-      <c r="F46" s="2" t="n"/>
-    </row>
-    <row r="47">
-      <c r="F47" s="2" t="n"/>
-    </row>
-    <row r="48">
-      <c r="F48" s="2" t="n"/>
-    </row>
-    <row r="49">
-      <c r="F49" s="2" t="n"/>
-    </row>
-    <row r="50">
-      <c r="F50" s="2" t="n"/>
-    </row>
-    <row r="51">
-      <c r="F51" s="2" t="n"/>
-    </row>
-    <row r="52">
-      <c r="F52" s="2" t="n"/>
-    </row>
-    <row r="53">
-      <c r="F53" s="2" t="n"/>
-    </row>
-    <row r="54">
-      <c r="F54" s="2" t="n"/>
-    </row>
-    <row r="55">
-      <c r="F55" s="2" t="n"/>
-    </row>
-    <row r="56">
-      <c r="F56" s="2" t="n"/>
-    </row>
-    <row r="57">
-      <c r="F57" s="2" t="n"/>
-    </row>
-    <row r="58">
-      <c r="F58" s="2" t="n"/>
-    </row>
-    <row r="59">
-      <c r="F59" s="2" t="n"/>
+          <t>30 seg</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B2:B200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Calistenia,Proyecto"</formula1>
+    <dataValidation sqref="A2:A100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1187,285 +1061,227 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Contexto</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Fecha</t>
+          <t>Proyecto</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Valor</t>
+          <t>Hito</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Orden</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Dominadas seguidas</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>4</v>
+          <t>Estudio</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Sprint Diseño</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Investigación inicial</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Inicio</t>
-        </is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dominadas seguidas</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>5</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>Estudio</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Sprint Diseño</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Marco teórico</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Dominadas seguidas</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>6</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Estudio</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Sprint Diseño</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Prototipo funcional</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Avance del proyecto</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Estudio</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sprint Diseño</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Entrega final</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Avance del proyecto</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>35</v>
+          <t>Calistenia</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dominadas</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>5 dominadas seguidas</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Módulo de datos listo</t>
-        </is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="2" t="n"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Calistenia</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dominadas</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>8 dominadas seguidas</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
-      <c r="B8" s="2" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="2" t="n"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="2" t="n"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="2" t="n"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="2" t="n"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="2" t="n"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="2" t="n"/>
-    </row>
-    <row r="15">
-      <c r="B15" s="2" t="n"/>
-    </row>
-    <row r="16">
-      <c r="B16" s="2" t="n"/>
-    </row>
-    <row r="17">
-      <c r="B17" s="2" t="n"/>
-    </row>
-    <row r="18">
-      <c r="B18" s="2" t="n"/>
-    </row>
-    <row r="19">
-      <c r="B19" s="2" t="n"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="2" t="n"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="2" t="n"/>
-    </row>
-    <row r="22">
-      <c r="B22" s="2" t="n"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="2" t="n"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="2" t="n"/>
-    </row>
-    <row r="25">
-      <c r="B25" s="2" t="n"/>
-    </row>
-    <row r="26">
-      <c r="B26" s="2" t="n"/>
-    </row>
-    <row r="27">
-      <c r="B27" s="2" t="n"/>
-    </row>
-    <row r="28">
-      <c r="B28" s="2" t="n"/>
-    </row>
-    <row r="29">
-      <c r="B29" s="2" t="n"/>
-    </row>
-    <row r="30">
-      <c r="B30" s="2" t="n"/>
-    </row>
-    <row r="31">
-      <c r="B31" s="2" t="n"/>
-    </row>
-    <row r="32">
-      <c r="B32" s="2" t="n"/>
-    </row>
-    <row r="33">
-      <c r="B33" s="2" t="n"/>
-    </row>
-    <row r="34">
-      <c r="B34" s="2" t="n"/>
-    </row>
-    <row r="35">
-      <c r="B35" s="2" t="n"/>
-    </row>
-    <row r="36">
-      <c r="B36" s="2" t="n"/>
-    </row>
-    <row r="37">
-      <c r="B37" s="2" t="n"/>
-    </row>
-    <row r="38">
-      <c r="B38" s="2" t="n"/>
-    </row>
-    <row r="39">
-      <c r="B39" s="2" t="n"/>
-    </row>
-    <row r="40">
-      <c r="B40" s="2" t="n"/>
-    </row>
-    <row r="41">
-      <c r="B41" s="2" t="n"/>
-    </row>
-    <row r="42">
-      <c r="B42" s="2" t="n"/>
-    </row>
-    <row r="43">
-      <c r="B43" s="2" t="n"/>
-    </row>
-    <row r="44">
-      <c r="B44" s="2" t="n"/>
-    </row>
-    <row r="45">
-      <c r="B45" s="2" t="n"/>
-    </row>
-    <row r="46">
-      <c r="B46" s="2" t="n"/>
-    </row>
-    <row r="47">
-      <c r="B47" s="2" t="n"/>
-    </row>
-    <row r="48">
-      <c r="B48" s="2" t="n"/>
-    </row>
-    <row r="49">
-      <c r="B49" s="2" t="n"/>
-    </row>
-    <row r="50">
-      <c r="B50" s="2" t="n"/>
-    </row>
-    <row r="51">
-      <c r="B51" s="2" t="n"/>
-    </row>
-    <row r="52">
-      <c r="B52" s="2" t="n"/>
-    </row>
-    <row r="53">
-      <c r="B53" s="2" t="n"/>
-    </row>
-    <row r="54">
-      <c r="B54" s="2" t="n"/>
-    </row>
-    <row r="55">
-      <c r="B55" s="2" t="n"/>
-    </row>
-    <row r="56">
-      <c r="B56" s="2" t="n"/>
-    </row>
-    <row r="57">
-      <c r="B57" s="2" t="n"/>
-    </row>
-    <row r="58">
-      <c r="B58" s="2" t="n"/>
-    </row>
-    <row r="59">
-      <c r="B59" s="2" t="n"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Calistenia</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dominadas</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>12 dominadas seguidas</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="A2:A100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Estudio,Calistenia"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Hecho,Actual,Pendiente"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>